--- a/data/trans_orig/Q70-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q70-Habitat-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,66</t>
+          <t>6,3</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,27</t>
+          <t>8,01</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,36</t>
+          <t>7,04</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,72</t>
+          <t>0,44; 2,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,72</t>
+          <t>0,64; 2,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 8,32</t>
+          <t>0,73; 7,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,94; 11,88</t>
+          <t>3,65; 11,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 6,5</t>
+          <t>0,43; 5,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 6,46</t>
+          <t>0,46; 6,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 12,49</t>
+          <t>1,15; 11,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,91; 12,51</t>
+          <t>5,71; 12,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,33</t>
+          <t>0,52; 2,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,22</t>
+          <t>0,69; 3,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 7,32</t>
+          <t>1,37; 6,84</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,37; 10,46</t>
+          <t>5,18; 10,33</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,68</t>
+          <t>7,89</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,53</t>
+          <t>9,16</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,95</t>
+          <t>8,42</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,75</t>
+          <t>0,87; 1,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 6,95</t>
+          <t>1,4; 7,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,72</t>
+          <t>1,48; 5,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,47; 9,54</t>
+          <t>5,3; 13,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 8,94</t>
+          <t>0,78; 9,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 9,87</t>
+          <t>0,93; 9,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,64</t>
+          <t>0,26; 3,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,7; 13,86</t>
+          <t>6,76; 12,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,65</t>
+          <t>0,99; 3,97</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 6,3</t>
+          <t>1,71; 6,34</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,85</t>
+          <t>1,26; 3,92</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,1; 10,03</t>
+          <t>6,36; 11,61</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,69</t>
+          <t>4,64</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,56</t>
+          <t>6,58</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,11</t>
+          <t>5,51</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,1</t>
+          <t>1,14; 5,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,5</t>
+          <t>0,37; 1,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,67</t>
+          <t>0,6; 1,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,57; 9,82</t>
+          <t>3,02; 7,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 6,05</t>
+          <t>1,55; 6,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,13</t>
+          <t>0,43; 2,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,92</t>
+          <t>1,21; 5,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,07; 10,05</t>
+          <t>4,69; 10,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,43</t>
+          <t>1,49; 4,08</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,62</t>
+          <t>0,5; 1,62</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,78</t>
+          <t>0,96; 2,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,27; 8,61</t>
+          <t>4,28; 7,53</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,26</t>
+          <t>5,81</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,93</t>
+          <t>9,22</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,11</t>
+          <t>7,4</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,6</t>
+          <t>0,87; 2,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,74</t>
+          <t>0,76; 1,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 5,74</t>
+          <t>1,21; 5,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,38; 9,74</t>
+          <t>4,04; 9,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,41</t>
+          <t>0,85; 2,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,88</t>
+          <t>0,78; 3,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,14</t>
+          <t>0,99; 3,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,68; 11,39</t>
+          <t>6,62; 12,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,13</t>
+          <t>0,92; 1,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,15</t>
+          <t>0,9; 2,19</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,88</t>
+          <t>1,4; 4,23</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,22; 9,28</t>
+          <t>5,68; 9,81</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,98</t>
+          <t>6,33</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,13</t>
+          <t>8,4</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,9</t>
+          <t>7,24</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,05</t>
+          <t>1,08; 2,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,74</t>
+          <t>1,12; 2,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,55</t>
+          <t>1,39; 3,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,19; 7,79</t>
+          <t>5,07; 8,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,29</t>
+          <t>1,26; 3,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,77</t>
+          <t>1,14; 3,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,38</t>
+          <t>1,29; 3,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,23; 9,95</t>
+          <t>7,1; 10,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,15</t>
+          <t>1,23; 2,19</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,59</t>
+          <t>1,24; 2,6</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,94</t>
+          <t>1,57; 2,9</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,34</t>
+          <t>6,26; 8,64</t>
         </is>
       </c>
     </row>
